--- a/資料/クラスデータ/黒い砂漠M_スキル・パッシブ.xlsx
+++ b/資料/クラスデータ/黒い砂漠M_スキル・パッシブ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cloude cowork\スキル秘伝HP\skill-sigil-web\資料\クラスデータ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B0C534-D046-4D82-9F73-71BF4CA7089B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D917C6-E0CC-4A7D-88E9-626793961EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28545" yWindow="2220" windowWidth="26055" windowHeight="11985" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28290" yWindow="630" windowWidth="26055" windowHeight="11985" firstSheet="23" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス一覧" sheetId="1" r:id="rId1"/>
@@ -39999,7 +39999,7 @@
         <v>3801</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>8</v>
